--- a/donation_forms/038_donor_referral_source_survey--donation_forms.xlsx
+++ b/donation_forms/038_donor_referral_source_survey--donation_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -515,17 +515,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>referral_source_1</t>
+          <t>motivated_to_support</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>How Did You Hear About Us</t>
+          <t>What motivated you to support our organization?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -538,17 +538,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>referral_source_2</t>
+          <t>referred_someone</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>How Did You Hear About Us</t>
+          <t>Have you referred anyone to our organization before?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,17 +561,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>referral_source_3</t>
+          <t>initial_heard_about</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>How Did You Hear About Us</t>
+          <t>How did you hear about us initially?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -589,18 +589,18 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>referral_source_4</t>
+          <t>interacted_with_organization</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>How Did You Hear About Us</t>
+          <t>Have you ever interacted with our organization through social media?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -612,18 +612,18 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>referral_source_5</t>
+          <t>has_friend_support</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>How Did You Hear About Us</t>
+          <t>Do you have any friends or family members who support our organization?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -635,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>referral_source_6</t>
+          <t>referral_info</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>How Did You Hear About Us</t>
+          <t>What is your contact information for the person who referred you to our organization?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -658,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>referral_source_7</t>
+          <t>heard_mission_values</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>How Did You Hear About Us</t>
+          <t>How did you hear about our organization's mission or values?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,46 +676,46 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>referral_source_8</t>
+          <t>attended_event</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>How Did You Hear About Us</t>
+          <t>Have you ever attended an event hosted by our organization?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>referral_source_9</t>
+          <t>heard_event_info</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>How Did You Hear About Us</t>
+          <t>How did you hear about our organization's events?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -727,248 +727,18 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>referral_source_10</t>
+          <t>comments</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>How Did You Hear About Us</t>
+          <t>Do you have any other questions or comments about our organization?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>referral_source_11</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>How Did You Hear About Us</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>referral_source_12</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>How Did You Hear About Us</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>referral_source_13</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>How Did You Hear About Us</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>referral_source_14</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>How Did You Hear About Us</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>referral_source_15</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>How Did You Hear About Us</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>referral_source_16</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>How Did You Hear About Us</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>referral_source_17</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>How Did You Hear About Us</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>referral_source_18</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>How Did You Hear About Us</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>referral_source_19</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>How Did You Hear About Us</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>referral_source_20</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>How Did You Hear About Us</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -983,10 +753,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:C50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="38" customWidth="1" min="1" max="1"/>
     <col width="41" customWidth="1" min="2" max="2"/>
     <col width="41" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1011,7 +781,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>referral_source_2_choices</t>
+          <t>motivated_to_support_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1028,7 +798,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>referral_source_2_choices</t>
+          <t>motivated_to_support_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1045,7 +815,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>referral_source_2_choices</t>
+          <t>motivated_to_support_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1062,7 +832,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>referral_source_2_choices</t>
+          <t>motivated_to_support_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1079,92 +849,92 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>referral_source_2_choices</t>
+          <t>motivated_to_support_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>word_of_mouth</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Word of mouth</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>referral_source_2_choices</t>
+          <t>motivated_to_support_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>word_of_mouth</t>
+          <t>volunteer</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Word of mouth</t>
+          <t>Volunteer</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>referral_source_2_choices</t>
+          <t>motivated_to_support_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>volunteer</t>
+          <t>event</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Volunteer</t>
+          <t>Event</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>referral_source_2_choices</t>
+          <t>motivated_to_support_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>radio_or_tv_ad</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>Radio or TV ad</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>referral_source_2_choices</t>
+          <t>motivated_to_support_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>radio_or_tv_ad</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Radio or TV ad</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>referral_source_3_choices</t>
+          <t>referred_someone_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1181,7 +951,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>referral_source_3_choices</t>
+          <t>referred_someone_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1198,7 +968,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>referral_source_3_choices</t>
+          <t>referred_someone_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1215,7 +985,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>referral_source_3_choices</t>
+          <t>referred_someone_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1232,92 +1002,92 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>referral_source_3_choices</t>
+          <t>initial_heard_about_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>word_of_mouth</t>
+          <t>donor_newsletter</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Word of mouth</t>
+          <t>Donor Newsletter</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>referral_source_3_choices</t>
+          <t>initial_heard_about_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>volunteer</t>
+          <t>social_media</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Volunteer</t>
+          <t>Social Media</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>referral_source_3_choices</t>
+          <t>initial_heard_about_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>referral_from_a_friend_or_family_member</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>Referral from a friend or family member</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>referral_source_3_choices</t>
+          <t>initial_heard_about_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>online_search</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Online search</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>referral_source_3_choices</t>
+          <t>initial_heard_about_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>radio_or_tv_ad</t>
+          <t>word_of_mouth</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Radio or TV ad</t>
+          <t>Word of mouth</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>referral_source_4_choices</t>
+          <t>initial_heard_about_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1334,7 +1104,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>referral_source_4_choices</t>
+          <t>initial_heard_about_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1351,136 +1121,493 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>referral_source_5_choices</t>
+          <t>initial_heard_about_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>radio_or_tv_ad</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Radio or TV ad</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>referral_source_5_choices</t>
+          <t>interacted_with_organization_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>facebook</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Facebook</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>referral_source_7_choices</t>
+          <t>interacted_with_organization_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>twitter</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Twitter</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>referral_source_7_choices</t>
+          <t>interacted_with_organization_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>instagram</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Instagram</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>referral_source_14_choices</t>
+          <t>interacted_with_organization_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>youtube</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>YouTube</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>referral_source_14_choices</t>
+          <t>interacted_with_organization_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>linkedin</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>LinkedIn</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>referral_source_20_choices</t>
+          <t>interacted_with_organization_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>referral_source_20_choices</t>
+          <t>has_friend_support_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>has_friend_support_choices</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>heard_mission_values_choices</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>donor_newsletter</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Donor Newsletter</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>heard_mission_values_choices</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>social_media</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Social Media</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>heard_mission_values_choices</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>referral_from_a_friend_or_family_member</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Referral from a friend or family member</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>heard_mission_values_choices</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>online_search</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Online search</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>heard_mission_values_choices</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>word_of_mouth</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Word of mouth</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>heard_mission_values_choices</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>volunteer</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Volunteer</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>heard_mission_values_choices</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>heard_mission_values_choices</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>radio_or_tv_ad</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Radio or TV ad</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>heard_mission_values_choices</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>attended_event_choices</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>attended_event_choices</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>heard_event_info_choices</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>donor_newsletter</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Donor Newsletter</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>heard_event_info_choices</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>social_media</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Social Media</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>heard_event_info_choices</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>referral_from_a_friend_or_family_member</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Referral from a friend or family member</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>heard_event_info_choices</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>online_search</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Online search</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>heard_event_info_choices</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>word_of_mouth</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Word of mouth</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>heard_event_info_choices</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>volunteer</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Volunteer</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>heard_event_info_choices</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>heard_event_info_choices</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>radio_or_tv_ad</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Radio or TV ad</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>heard_event_info_choices</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Other</t>
         </is>
       </c>
     </row>
